--- a/artfynd/A 17770-2026 artfynd.xlsx
+++ b/artfynd/A 17770-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132426909</v>
+        <v>132426939</v>
       </c>
       <c r="B2" t="n">
-        <v>57957</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Getklövmyran, Getklövmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579075</v>
+        <v>579073</v>
       </c>
       <c r="R2" t="n">
-        <v>7052526</v>
+        <v>7052518</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132426939</v>
+        <v>132427040</v>
       </c>
       <c r="B3" t="n">
-        <v>92216</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579073</v>
+        <v>579091</v>
       </c>
       <c r="R3" t="n">
-        <v>7052518</v>
+        <v>7052498</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,54 +889,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132426369</v>
+        <v>132427116</v>
       </c>
       <c r="B4" t="n">
-        <v>58118</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Getklövmyran, Getklövmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578856</v>
+        <v>579132</v>
       </c>
       <c r="R4" t="n">
-        <v>7052309</v>
+        <v>7052472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -988,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,45 +996,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132427040</v>
+        <v>132426455</v>
       </c>
       <c r="B5" t="n">
-        <v>79332</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövmyran, Getklövmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579091</v>
+        <v>578870</v>
       </c>
       <c r="R5" t="n">
-        <v>7052498</v>
+        <v>7052344</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1075,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1085,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1122,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132427116</v>
+        <v>132426909</v>
       </c>
       <c r="B6" t="n">
-        <v>79332</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,34 +1123,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Getklövmyran, Getklövmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579132</v>
+        <v>579075</v>
       </c>
       <c r="R6" t="n">
-        <v>7052472</v>
+        <v>7052526</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1192,7 +1187,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1202,7 +1197,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132426455</v>
+        <v>134113905</v>
       </c>
       <c r="B7" t="n">
-        <v>57954</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1257,14 +1257,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1273,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578870</v>
+        <v>579151</v>
       </c>
       <c r="R7" t="n">
-        <v>7052344</v>
+        <v>7052413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,22 +1299,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,10 +1346,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134113905</v>
+        <v>132426369</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>58136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,27 +1357,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1385,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579151</v>
+        <v>578856</v>
       </c>
       <c r="R8" t="n">
-        <v>7052413</v>
+        <v>7052309</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1415,27 +1420,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 17770-2026 artfynd.xlsx
+++ b/artfynd/A 17770-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132427040</v>
+        <v>135484913</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>92153</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Getklövmyran, Getklövmyran, Ång</t>
+          <t>1 km öst om Nedre Strömnäs, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579091</v>
+        <v>578806</v>
       </c>
       <c r="R3" t="n">
-        <v>7052498</v>
+        <v>7052166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -873,23 +863,40 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>gammal naturskogsartad tallskog på storblockig höjd</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hängande tallåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132427116</v>
+        <v>132427040</v>
       </c>
       <c r="B4" t="n">
         <v>79373</v>
@@ -924,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579132</v>
+        <v>579091</v>
       </c>
       <c r="R4" t="n">
-        <v>7052472</v>
+        <v>7052498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +966,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +976,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,54 +1003,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132426455</v>
+        <v>132427116</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövmyran, Getklövmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578870</v>
+        <v>579132</v>
       </c>
       <c r="R5" t="n">
-        <v>7052344</v>
+        <v>7052472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1075,7 +1073,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1085,7 +1083,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,27 +1110,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132426909</v>
+        <v>132426455</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1140,10 +1138,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1152,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579075</v>
+        <v>578870</v>
       </c>
       <c r="R6" t="n">
-        <v>7052526</v>
+        <v>7052344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1187,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1197,12 +1199,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,7 +1226,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134113905</v>
+        <v>132426909</v>
       </c>
       <c r="B7" t="n">
         <v>57975</v>
@@ -1260,7 +1257,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1269,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579151</v>
+        <v>579075</v>
       </c>
       <c r="R7" t="n">
-        <v>7052413</v>
+        <v>7052526</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1299,27 +1296,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132426369</v>
+        <v>134113905</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,31 +1354,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1390,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578856</v>
+        <v>579151</v>
       </c>
       <c r="R8" t="n">
-        <v>7052309</v>
+        <v>7052413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,22 +1413,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,6 +1457,122 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132426369</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>578856</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7052309</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17770-2026 artfynd.xlsx
+++ b/artfynd/A 17770-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132426939</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135484913</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132427040</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132427116</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132426455</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1340,6 +1370,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132426909</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113905</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1573,8 +1613,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132426369</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 17770-2026 artfynd.xlsx
+++ b/artfynd/A 17770-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135484913</v>
       </c>
       <c r="B3" t="n">
-        <v>92153</v>
+        <v>92195</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17770-2026 artfynd.xlsx
+++ b/artfynd/A 17770-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135484913</v>
       </c>
       <c r="B3" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17770-2026 artfynd.xlsx
+++ b/artfynd/A 17770-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132427040</v>
+        <v>135484913</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>92227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Getklövmyran, Getklövmyran, Ång</t>
+          <t>1 km öst om Nedre Strömnäs, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579091</v>
+        <v>578806</v>
       </c>
       <c r="R3" t="n">
-        <v>7052498</v>
+        <v>7052166</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:10</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,28 +873,45 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>gammal naturskogsartad tallskog på storblockig höjd</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>1 substratenheter # gammal hängande tallåga</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132427040</t>
+          <t>https://artportalen.se/Sighting/135484913</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132427116</v>
+        <v>132427040</v>
       </c>
       <c r="B4" t="n">
         <v>79373</v>
@@ -939,10 +946,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579132</v>
+        <v>579091</v>
       </c>
       <c r="R4" t="n">
-        <v>7052472</v>
+        <v>7052498</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,60 +1017,51 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132427116</t>
+          <t>https://artportalen.se/Sighting/132427040</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132426455</v>
+        <v>132427116</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Getklövmyran, Getklövmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578870</v>
+        <v>579132</v>
       </c>
       <c r="R5" t="n">
-        <v>7052344</v>
+        <v>7052472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,33 +1129,33 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132426455</t>
+          <t>https://artportalen.se/Sighting/132427116</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132426909</v>
+        <v>132426455</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1165,10 +1163,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1177,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579075</v>
+        <v>578870</v>
       </c>
       <c r="R6" t="n">
-        <v>7052526</v>
+        <v>7052344</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1214,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,12 +1224,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,13 +1250,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132426909</t>
+          <t>https://artportalen.se/Sighting/132426455</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134113905</v>
+        <v>132426909</v>
       </c>
       <c r="B7" t="n">
         <v>57975</v>
@@ -1290,7 +1287,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1296,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579151</v>
+        <v>579075</v>
       </c>
       <c r="R7" t="n">
-        <v>7052413</v>
+        <v>7052526</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,27 +1326,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,16 +1372,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134113905</t>
+          <t>https://artportalen.se/Sighting/132426909</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132426369</v>
+        <v>134113905</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,31 +1389,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1425,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>578856</v>
+        <v>579151</v>
       </c>
       <c r="R8" t="n">
-        <v>7052309</v>
+        <v>7052413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,22 +1448,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,6 +1493,127 @@
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134113905</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132426369</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Getklövmyran, Getklövmyran, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>578856</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7052309</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132426369</t>
         </is>
@@ -1509,6 +1628,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17770-2026 artfynd.xlsx
+++ b/artfynd/A 17770-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135484913</v>
       </c>
       <c r="B3" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17770-2026 artfynd.xlsx
+++ b/artfynd/A 17770-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135484913</v>
       </c>
       <c r="B3" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 17770-2026 artfynd.xlsx
+++ b/artfynd/A 17770-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>135484913</v>
       </c>
       <c r="B3" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
